--- a/data/outputs/weight_analysis.xlsx
+++ b/data/outputs/weight_analysis.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,7 +554,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>소음·진동저감</t>
+          <t>지하수위제어</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -658,17 +658,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>난징 지하철 line 10</t>
+          <t>Marmaray Project – Üsküdar</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>4.78</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>매우높음</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>소음·진동저감</t>
+          <t>지하수위제어</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -704,17 +704,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gotthard Base Tunnel(고트하르트 베이스 터널)</t>
+          <t>Folgefonna Tunnel</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2450</v>
+        <v>500</v>
       </c>
       <c r="C7" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>57</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -728,17 +728,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>보통</t>
+          <t>낮음</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>안정성·시공성</t>
+          <t>고지압</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>소음·진동저감</t>
+          <t>지하수위제어</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>55</v>
+        <v>32.5</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>소음·진동저감</t>
+          <t>지하수위제어</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -972,6 +972,144 @@
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>침매식</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Varberg Tunnel (West Coast Line)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>25</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>암반</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>지하수위제어</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>지하수위제어</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NATM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fehmarnbelt Fixed Link</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>40</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>수중</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>수밀·방수</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>장기안정성</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>침매식</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Hong Kong–Zhuhai–Macao Bridge Immersed Tunnel</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>45</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>수중</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>수밀·방수</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>지하수위제어</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>침매식</t>
         </is>
@@ -1011,27 +1149,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>시공 위치_정규화</t>
+          <t>요구사항_주요정규화</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9949236325717751</v>
+        <v>0.8809501562890273</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1901103785868279</v>
+        <v>0.1878957713484992</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>심도(m)_정규화</t>
+          <t>시공 위치_정규화</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9364718614718618</v>
+        <v>0.8760057656431735</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1789413923761466</v>
+        <v>0.1868411939837996</v>
       </c>
     </row>
     <row r="4">
@@ -1041,68 +1179,68 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8688968724699669</v>
+        <v>0.8122878903508541</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1660291382879172</v>
+        <v>0.1732509593476304</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>주변 민감도_정규화</t>
+          <t>심도(m)_정규화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8380061385071674</v>
+        <v>0.613142413142413</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1601265253272494</v>
+        <v>0.1307756924060028</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>요구사항_주요정규화</t>
+          <t>지반 조건_정규화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6953020992986543</v>
+        <v>0.5465122114944402</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1328585843198849</v>
+        <v>0.1165642945824414</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>지반 조건_정규화</t>
+          <t>주변 민감도_정규화</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4908165921645422</v>
+        <v>0.504192953436833</v>
       </c>
       <c r="C7" t="n">
-        <v>0.09378541739118491</v>
+        <v>0.1075381203104188</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>터널 길이(km)_정규화</t>
+          <t>구경(m)_정규화</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4089826839826844</v>
+        <v>0.4554130393416107</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07814856371078914</v>
+        <v>0.09713396802120779</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>구경(m)_정규화</t>
+          <t>터널 길이(km)_정규화</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1150,101 +1288,101 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.864764230325818</v>
+        <v>1.91759292781353</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3248144687377256</v>
+        <v>0.290156453936399</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>주변 민감도_정규화</t>
+          <t>요구사항_주요정규화</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.088062644004822</v>
+        <v>1.530782133340836</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1895244899694589</v>
+        <v>0.2316270096311933</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>요구사항_주요정규화</t>
+          <t>지반 조건_정규화</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9307916760444641</v>
+        <v>1.079932510852814</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1621302032949521</v>
+        <v>0.1634076676518463</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>지반 조건_정규화</t>
+          <t>주변 민감도_정규화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7370148003101349</v>
+        <v>0.6998069584369659</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1283771250656979</v>
+        <v>0.1058897863852741</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>심도(m)_정규화</t>
+          <t>구경(m)_정규화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.567677915096283</v>
+        <v>0.5334550738334656</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09888113328617505</v>
+        <v>0.08071860837241776</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>터널 길이(km)_정규화</t>
+          <t>심도(m)_정규화</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2507699728012085</v>
+        <v>0.4942696988582611</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04368043646813547</v>
+        <v>0.0747893575475633</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>구경(m)_정규화</t>
+          <t>요구사항_보조정규화</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1758742481470108</v>
+        <v>0.2210694551467896</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03063470413444004</v>
+        <v>0.03345064963927621</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>요구사항_보조정규화</t>
+          <t>터널 길이(km)_정규화</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1260579526424408</v>
+        <v>0.1319152116775513</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02195743904341497</v>
+        <v>0.01996046683603005</v>
       </c>
     </row>
   </sheetData>
@@ -1300,19 +1438,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8688968724699669</v>
+        <v>0.8122878903508541</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1660291382879172</v>
+        <v>0.1732509593476304</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1260579526424408</v>
+        <v>0.2210694551467896</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02195743904341497</v>
+        <v>0.03345064963927621</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1440716992445022</v>
+        <v>0.1398003097083542</v>
       </c>
     </row>
     <row r="3">
@@ -1322,19 +1460,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9949236325717751</v>
+        <v>0.8760057656431735</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1901103785868279</v>
+        <v>0.1868411939837996</v>
       </c>
       <c r="D3" t="n">
-        <v>1.864764230325818</v>
+        <v>1.91759292781353</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3248144687377256</v>
+        <v>0.290156453936399</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1347040901508977</v>
+        <v>0.1033152599525994</v>
       </c>
     </row>
     <row r="4">
@@ -1344,19 +1482,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9364718614718618</v>
+        <v>0.613142413142413</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1789413923761466</v>
+        <v>0.1307756924060028</v>
       </c>
       <c r="D4" t="n">
-        <v>0.567677915096283</v>
+        <v>0.4942696988582611</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09888113328617505</v>
+        <v>0.0747893575475633</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08006025908997154</v>
+        <v>0.05598633485843946</v>
       </c>
     </row>
     <row r="5">
@@ -1366,47 +1504,47 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4908165921645422</v>
+        <v>0.5465122114944402</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09378541739118491</v>
+        <v>0.1165642945824414</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7370148003101349</v>
+        <v>1.079932510852814</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1283771250656979</v>
+        <v>0.1634076676518463</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03459170767451296</v>
+        <v>0.04684337306940485</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>터널 길이(km)_정규화</t>
+          <t>요구사항_주요정규화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4089826839826844</v>
+        <v>0.8809501562890273</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07814856371078914</v>
+        <v>0.1878957713484992</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2507699728012085</v>
+        <v>1.530782133340836</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04368043646813547</v>
+        <v>0.2316270096311933</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03446812724265367</v>
+        <v>0.0437312382826941</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>구경(m)_정규화</t>
+          <t>터널 길이(km)_정규화</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1416,57 +1554,57 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1758742481470108</v>
+        <v>0.1319152116775513</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03063470413444004</v>
+        <v>0.01996046683603005</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03063470413444004</v>
+        <v>0.01996046683603005</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>주변 민감도_정규화</t>
+          <t>구경(m)_정규화</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8380061385071674</v>
+        <v>0.4554130393416107</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1601265253272494</v>
+        <v>0.09713396802120779</v>
       </c>
       <c r="D8" t="n">
-        <v>1.088062644004822</v>
+        <v>0.5334550738334656</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1895244899694589</v>
+        <v>0.08071860837241776</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02939796464220948</v>
+        <v>0.01641535964879003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>요구사항_주요정규화</t>
+          <t>주변 민감도_정규화</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6953020992986543</v>
+        <v>0.504192953436833</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1328585843198849</v>
+        <v>0.1075381203104188</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9307916760444641</v>
+        <v>0.6998069584369659</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1621302032949521</v>
+        <v>0.1058897863852741</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02927161897506722</v>
+        <v>0.001648333925144768</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/weight_analysis.xlsx
+++ b/data/outputs/weight_analysis.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,7 +554,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>지하수위제어</t>
+          <t>지하수제어</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>지하수위제어</t>
+          <t>지하수제어</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>지하수위제어</t>
+          <t>지하수제어</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1106,12 +1106,1162 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>지하수제어</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>침매식</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Crossrail C300 Western Running Tunnels</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>30</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>지하수제어</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Barcelona Metro Line 9 (L9 South)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>25</v>
+      </c>
+      <c r="C17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>도시복합</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>대구경 안정성</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Delhi Metro Phase III Underground</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>지하수제어</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Guangzhou Metro Line 3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>지하수제어</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Shanghai Metro Line 7</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>20</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>지하수제어</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Thames Tideway Tunnel</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>35</v>
+      </c>
+      <c r="C21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>25</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>지하수제어</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Slurry TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Shanghai Yangtze River Tunnel</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>40</v>
+      </c>
+      <c r="C22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>수중</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>대구경 안정성</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Slurry TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Nanjing Yangtze River Tunnel</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>50</v>
+      </c>
+      <c r="C23" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>수중</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>지반안정성</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Slurry TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Busan Subway Line 2 River Crossing</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>30</v>
+      </c>
+      <c r="C24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>수중</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>지하수제어</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Slurry TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Guangzhou Pearl River Tunnel</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>35</v>
+      </c>
+      <c r="C25" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>수중</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>굴진안정성</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Slurry TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kishanganga Hydropower Tunnel</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C26" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>암반</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>산악</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>고지압</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>지하수제어</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NATM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Niagara Tunnel Project (NATM section)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>140</v>
+      </c>
+      <c r="C27" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>암반</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>도시복합</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>고수압</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>내구성·안정성</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>NATM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ghomri Tunnel</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>300</v>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>암반</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>산악</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>고지압</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>지반안정성</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NATM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Qinghai-Tibet Railway Tunnel Section</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>600</v>
+      </c>
+      <c r="C29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>암반</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>산악</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>동결지반·고지압</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>지반보강</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NATM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Alborz Tunnel</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>800</v>
+      </c>
+      <c r="C30" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>암반</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>산악</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>고지압</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>지반보강</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NATM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Hong Kong–Zhuhai–Macao Bridge Tunnel</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>수중</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>수밀·방수</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>접합부 방수관리</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>침매식</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Fehmarnbelt Fixed Link</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>40</v>
+      </c>
+      <c r="C32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>18</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>수중</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>낮음</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>수밀·방수</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>내구성·장기안정성</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>침매식</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Tsuen Wan Line Immersed Tube</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>수중</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>수밀·방수</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>시공정밀도</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>침매식</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Transbay Tube</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>41</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>수중</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>수밀·방수</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>내진·접합부관리</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>침매식</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Limfjord Tunnel (immersed section)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>수중</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>중간</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>수밀·방수</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>부력·안정성</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>침매식</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Second Avenue Subway Phase 1 (Cut &amp; Cover)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>20</v>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>지하수제어</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>개착식</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Singapore Downtown Line Stage 1 (Cut &amp; Cover)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>18</v>
+      </c>
+      <c r="C37" t="n">
+        <v>9</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>지하수위제어</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>침매식</t>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>개착식</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Berlin U5 Extension (Cut &amp; Cover)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>15</v>
+      </c>
+      <c r="C38" t="n">
+        <v>9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>문화재 보호</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>개착식</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Copenhagen Cityringen (Station Sections)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>20</v>
+      </c>
+      <c r="C39" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>지하수제어</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>개착식</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nanjing Metro Line 10 (Olympic–Zhongsheng)</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>8</v>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>지하수제어</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>개착식</t>
         </is>
       </c>
     </row>
@@ -1153,36 +2303,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8809501562890273</v>
+        <v>1.040553645936589</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1878957713484992</v>
+        <v>0.2026350265682765</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>시공 위치_정규화</t>
+          <t>요구사항_보조정규화</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8760057656431735</v>
+        <v>0.8857028318688899</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1868411939837996</v>
+        <v>0.1724797347721632</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>요구사항_보조정규화</t>
+          <t>시공 위치_정규화</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8122878903508541</v>
+        <v>0.7670897370107697</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1732509593476304</v>
+        <v>0.1493812931667936</v>
       </c>
     </row>
     <row r="5">
@@ -1192,49 +2342,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.613142413142413</v>
+        <v>0.6658520121865263</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1307756924060028</v>
+        <v>0.129666491205759</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>지반 조건_정규화</t>
+          <t>주변 민감도_정규화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5465122114944402</v>
+        <v>0.6187573660755248</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1165642945824414</v>
+        <v>0.1204953880116158</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>주변 민감도_정규화</t>
+          <t>구경(m)_정규화</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.504192953436833</v>
+        <v>0.5951155393217926</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1075381203104188</v>
+        <v>0.115891432981452</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>구경(m)_정규화</t>
+          <t>지반 조건_정규화</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4554130393416107</v>
+        <v>0.3998251365310748</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09713396802120779</v>
+        <v>0.0778610285784116</v>
       </c>
     </row>
     <row r="9">
@@ -1244,10 +2394,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.1622161721846398</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.03158960471552828</v>
       </c>
     </row>
   </sheetData>
@@ -1284,27 +2434,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>시공 위치_정규화</t>
+          <t>요구사항_주요정규화</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.91759292781353</v>
+        <v>5.199420809745789</v>
       </c>
       <c r="C2" t="n">
-        <v>0.290156453936399</v>
+        <v>0.3168971456587126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>요구사항_주요정규화</t>
+          <t>시공 위치_정규화</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.530782133340836</v>
+        <v>3.744552612304688</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2316270096311933</v>
+        <v>0.228225042370873</v>
       </c>
     </row>
     <row r="4">
@@ -1314,10 +2464,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.079932510852814</v>
+        <v>3.241692721843719</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1634076676518463</v>
+        <v>0.1975764625031617</v>
       </c>
     </row>
     <row r="5">
@@ -1327,62 +2477,62 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6998069584369659</v>
+        <v>1.990365535020828</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1058897863852741</v>
+        <v>0.1213098881481792</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>구경(m)_정규화</t>
+          <t>심도(m)_정규화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5334550738334656</v>
+        <v>1.007269024848938</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08071860837241776</v>
+        <v>0.06139158390233656</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>심도(m)_정규화</t>
+          <t>구경(m)_정규화</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4942696988582611</v>
+        <v>0.5790590643882751</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0747893575475633</v>
+        <v>0.03529280883141692</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>요구사항_보조정규화</t>
+          <t>터널 길이(km)_정규화</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2210694551467896</v>
+        <v>0.4077300727367401</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03345064963927621</v>
+        <v>0.02485055566329695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>터널 길이(km)_정규화</t>
+          <t>요구사항_보조정규화</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1319152116775513</v>
+        <v>0.2371920831501484</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01996046683603005</v>
+        <v>0.01445651292202314</v>
       </c>
     </row>
   </sheetData>
@@ -1438,151 +2588,151 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8122878903508541</v>
+        <v>0.8857028318688899</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1732509593476304</v>
+        <v>0.1724797347721632</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2210694551467896</v>
+        <v>0.2371920831501484</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03345064963927621</v>
+        <v>0.01445651292202314</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1398003097083542</v>
+        <v>0.1580232218501401</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>시공 위치_정규화</t>
+          <t>지반 조건_정규화</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8760057656431735</v>
+        <v>0.3998251365310748</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1868411939837996</v>
+        <v>0.0778610285784116</v>
       </c>
       <c r="D3" t="n">
-        <v>1.91759292781353</v>
+        <v>3.241692721843719</v>
       </c>
       <c r="E3" t="n">
-        <v>0.290156453936399</v>
+        <v>0.1975764625031617</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1033152599525994</v>
+        <v>0.1197154339247501</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>심도(m)_정규화</t>
+          <t>요구사항_주요정규화</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.613142413142413</v>
+        <v>1.040553645936589</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1307756924060028</v>
+        <v>0.2026350265682765</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4942696988582611</v>
+        <v>5.199420809745789</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0747893575475633</v>
+        <v>0.3168971456587126</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05598633485843946</v>
+        <v>0.1142621190904361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>지반 조건_정규화</t>
+          <t>구경(m)_정규화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5465122114944402</v>
+        <v>0.5951155393217926</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1165642945824414</v>
+        <v>0.115891432981452</v>
       </c>
       <c r="D5" t="n">
-        <v>1.079932510852814</v>
+        <v>0.5790590643882751</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1634076676518463</v>
+        <v>0.03529280883141692</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04684337306940485</v>
+        <v>0.08059862415003503</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>요구사항_주요정규화</t>
+          <t>시공 위치_정규화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8809501562890273</v>
+        <v>0.7670897370107697</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1878957713484992</v>
+        <v>0.1493812931667936</v>
       </c>
       <c r="D6" t="n">
-        <v>1.530782133340836</v>
+        <v>3.744552612304688</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2316270096311933</v>
+        <v>0.228225042370873</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0437312382826941</v>
+        <v>0.07884374920407933</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>터널 길이(km)_정규화</t>
+          <t>심도(m)_정규화</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.6658520121865263</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.129666491205759</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1319152116775513</v>
+        <v>1.007269024848938</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01996046683603005</v>
+        <v>0.06139158390233656</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01996046683603005</v>
+        <v>0.06827490730342242</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>구경(m)_정규화</t>
+          <t>터널 길이(km)_정규화</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4554130393416107</v>
+        <v>0.1622161721846398</v>
       </c>
       <c r="C8" t="n">
-        <v>0.09713396802120779</v>
+        <v>0.03158960471552828</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5334550738334656</v>
+        <v>0.4077300727367401</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08071860837241776</v>
+        <v>0.02485055566329695</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01641535964879003</v>
+        <v>0.006739049052231331</v>
       </c>
     </row>
     <row r="9">
@@ -1592,19 +2742,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.504192953436833</v>
+        <v>0.6187573660755248</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1075381203104188</v>
+        <v>0.1204953880116158</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6998069584369659</v>
+        <v>1.990365535020828</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1058897863852741</v>
+        <v>0.1213098881481792</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001648333925144768</v>
+        <v>0.0008145001365633536</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/weight_analysis.xlsx
+++ b/data/outputs/weight_analysis.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>EPB TBM</t>
+          <t>Slurry TBM</t>
         </is>
       </c>
     </row>
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>높음</t>
+          <t>낮음</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -570,13 +570,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="C4" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -595,12 +595,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>수밀·방수</t>
+          <t>수압·수밀관리</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>수밀성확보</t>
+          <t>지하수제어</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>7.45</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>7.75</v>
       </c>
       <c r="D8" t="n">
         <v>1.057</v>
@@ -784,7 +784,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>안전굴진</t>
+          <t>굴진안정성</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -800,13 +800,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="D9" t="n">
-        <v>16.2</v>
+        <v>12.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>8.5</v>
+        <v>22.74</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>10.79</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>8.5</v>
+        <v>18.33</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>수중</t>
+          <t>하천 하부</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>수중</t>
+          <t>하천 하부</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>수중</t>
+          <t>하천 하부</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>수중</t>
+          <t>하천 하부</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>고수압</t>
+          <t>수압·수밀관리</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1815,7 +1815,7 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>8.5</v>
+        <v>23.6</v>
       </c>
       <c r="D31" t="n">
         <v>6.7</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>수밀·방수</t>
+          <t>수압·수밀관리</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1861,7 +1861,7 @@
         <v>40</v>
       </c>
       <c r="C32" t="n">
-        <v>8.5</v>
+        <v>21.8</v>
       </c>
       <c r="D32" t="n">
         <v>18</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>수밀·방수</t>
+          <t>수압·수밀관리</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1907,7 +1907,7 @@
         <v>30</v>
       </c>
       <c r="C33" t="n">
-        <v>8.5</v>
+        <v>11.6</v>
       </c>
       <c r="D33" t="n">
         <v>1.4</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>수밀·방수</t>
+          <t>수압·수밀관리</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1953,7 +1953,7 @@
         <v>41</v>
       </c>
       <c r="C34" t="n">
-        <v>8.5</v>
+        <v>11.4</v>
       </c>
       <c r="D34" t="n">
         <v>5.8</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>수밀·방수</t>
+          <t>수압·수밀관리</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1999,10 +1999,10 @@
         <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>8.5</v>
+        <v>17.4</v>
       </c>
       <c r="D35" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>수밀·방수</t>
+          <t>수압·수밀관리</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2038,17 +2038,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Second Avenue Subway Phase 1 (Cut &amp; Cover)</t>
+          <t>FHWA Cut &amp; Cover Box Tunnel</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2057,12 +2057,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>도심지</t>
+          <t>도시복합</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>매우높음</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2084,17 +2084,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Singapore Downtown Line Stage 1 (Cut &amp; Cover)</t>
+          <t>Dublin Port Tunnel (Cut &amp; Cover Section)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C37" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="D37" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>매우높음</t>
+          <t>높음</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>지하수위제어</t>
+          <t>지하수제어</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2130,21 +2130,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Berlin U5 Extension (Cut &amp; Cover)</t>
+          <t>North-South Line Extension Singapore (Cut &amp; Cover Tunnel Section)</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>15</v>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>혼합지반</t>
+          <t>연약지반</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>문화재 보호</t>
+          <t>지하수제어</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2176,17 +2176,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Copenhagen Cityringen (Station Sections)</t>
+          <t>Delhi Metro Cut &amp; Cover Tunnel (India)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C39" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>0.096</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>8</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D40" t="n">
         <v>3.94</v>
@@ -2262,6 +2262,788 @@
       <c r="J40" t="inlineStr">
         <is>
           <t>개착식</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Shiraz Metro Line 3(SM3)</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>27</v>
+      </c>
+      <c r="C41" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="D41" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>내구성·안정성</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Nanchang Metro Line 4</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.007</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>안정성·시공성</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>안전굴진</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Grand Paris Express-line14</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>안전굴진</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Grand Paris Express-line15</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>25</v>
+      </c>
+      <c r="C44" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" t="n">
+        <v>75</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>하천 하부</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>수밀성확보</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Marmaray Tunnel (Kazliçeşme(유럽) ~ Ayrılıkçeşme(아시아) 지하 구간)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>30</v>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>도심지 및 해저 연결부</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Slurry TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>청계천 복원 지하도로</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5</v>
+      </c>
+      <c r="C46" t="n">
+        <v>11</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>도시복합</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>개착식</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Grand Paris Express Line 16</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>20</v>
+      </c>
+      <c r="C47" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>소음·진동저감</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Slurry TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>일본 도쿄만 아쿠아라인 (Tokyo Bay Aqua-Line)</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="D48" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>하천 하부</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>내구성·안정성</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Slurry TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Xinsen Avenue Tunnel, Chongqing (지중굴착 190 m 구간(K1+065~K1+255), 지중굴착 155 m 구간(K1+700~K1+855)을 제외한 나머지 구간)</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C49" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>도시복합</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>안정성·시공성</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>수밀성확보</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>개착식</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>영국 런던 실버타운 터널 (Silvertown Tunnel)</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>15</v>
+      </c>
+      <c r="C50" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>하천 하부</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>소음·진동저감</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Slurry TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>수도권 고속철도(SRT) 율현터널(수서~평택)</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>40</v>
+      </c>
+      <c r="C51" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>소음·진동저감</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>스페인 바르셀로나 지하철 9호선 (L9)</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>30</v>
+      </c>
+      <c r="C52" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>굴진안정성</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>이탈리아 로마 지하철 C노선 (Rome Metro Line C)</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>30</v>
+      </c>
+      <c r="C53" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>굴진안정성</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>서울 지하철 9호선 3단계 923공구</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>30</v>
+      </c>
+      <c r="C54" t="n">
+        <v>12</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>소음·진동저감</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>NATM</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>일본 도쿄 도심(오에도선 연장 구간)</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>30</v>
+      </c>
+      <c r="C55" t="n">
+        <v>7</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>연약지반</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>수압·수밀관리</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Delhi Tunnel (India)</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C56" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>매우높음</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>소음·진동저감</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Grand Paris Express Line 16</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>30</v>
+      </c>
+      <c r="C57" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D57" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>혼합지반</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>도심지</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>높음</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>침하·변형관리</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>공기단축</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>EPB TBM</t>
         </is>
       </c>
     </row>
@@ -2299,14 +3081,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>요구사항_주요정규화</t>
+          <t>시공 위치_정규화</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.040553645936589</v>
+        <v>0.8152201663233285</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2026350265682765</v>
+        <v>0.2038059405248022</v>
       </c>
     </row>
     <row r="3">
@@ -2316,23 +3098,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8857028318688899</v>
+        <v>0.7832845266423945</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1724797347721632</v>
+        <v>0.1958219953891117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>시공 위치_정규화</t>
+          <t>요구사항_주요정규화</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7670897370107697</v>
+        <v>0.6084318380223158</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1493812931667936</v>
+        <v>0.1521086304238837</v>
       </c>
     </row>
     <row r="5">
@@ -2342,10 +3124,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6658520121865263</v>
+        <v>0.5918627373935359</v>
       </c>
       <c r="C5" t="n">
-        <v>0.129666491205759</v>
+        <v>0.1479663369959274</v>
       </c>
     </row>
     <row r="6">
@@ -2355,10 +3137,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6187573660755248</v>
+        <v>0.5333896598625405</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1204953880116158</v>
+        <v>0.1333480031348663</v>
       </c>
     </row>
     <row r="7">
@@ -2368,10 +3150,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5951155393217926</v>
+        <v>0.3426556591120367</v>
       </c>
       <c r="C7" t="n">
-        <v>0.115891432981452</v>
+        <v>0.08566429262469563</v>
       </c>
     </row>
     <row r="8">
@@ -2381,10 +3163,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3998251365310748</v>
+        <v>0.3062467494100243</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0778610285784116</v>
+        <v>0.07656202505105686</v>
       </c>
     </row>
     <row r="9">
@@ -2394,10 +3176,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1622161721846398</v>
+        <v>0.01889102009804899</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03158960471552828</v>
+        <v>0.004722775855656162</v>
       </c>
     </row>
   </sheetData>
@@ -2434,40 +3216,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>요구사항_주요정규화</t>
+          <t>시공 위치_정규화</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.199420809745789</v>
+        <v>7.689625799655914</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3168971456587126</v>
+        <v>0.381012492905042</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>시공 위치_정규화</t>
+          <t>지반 조건_정규화</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.744552612304688</v>
+        <v>3.060022637248039</v>
       </c>
       <c r="C3" t="n">
-        <v>0.228225042370873</v>
+        <v>0.151620752913088</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>지반 조건_정규화</t>
+          <t>요구사항_보조정규화</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.241692721843719</v>
+        <v>2.762166917324066</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1975764625031617</v>
+        <v>0.1368623298986239</v>
       </c>
     </row>
     <row r="5">
@@ -2477,62 +3259,62 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.990365535020828</v>
+        <v>2.690399169921875</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1213098881481792</v>
+        <v>0.1333063170235745</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>심도(m)_정규화</t>
+          <t>요구사항_주요정규화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.007269024848938</v>
+        <v>1.486804008483887</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06139158390233656</v>
+        <v>0.07366950180579704</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>구경(m)_정규화</t>
+          <t>심도(m)_정규화</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5790590643882751</v>
+        <v>1.336945652961731</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03529280883141692</v>
+        <v>0.06624418526793617</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>터널 길이(km)_정규화</t>
+          <t>구경(m)_정규화</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4077300727367401</v>
+        <v>0.6202138662338257</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02485055566329695</v>
+        <v>0.03073091428175845</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>요구사항_보조정규화</t>
+          <t>터널 길이(km)_정규화</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.2371920831501484</v>
+        <v>0.5359050631523132</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01445651292202314</v>
+        <v>0.02655350590417983</v>
       </c>
     </row>
   </sheetData>
@@ -2584,45 +3366,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>요구사항_보조정규화</t>
+          <t>시공 위치_정규화</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8857028318688899</v>
+        <v>0.8152201663233285</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1724797347721632</v>
+        <v>0.2038059405248022</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2371920831501484</v>
+        <v>7.689625799655914</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01445651292202314</v>
+        <v>0.381012492905042</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1580232218501401</v>
+        <v>0.1772065523802398</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>지반 조건_정규화</t>
+          <t>심도(m)_정규화</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3998251365310748</v>
+        <v>0.5918627373935359</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0778610285784116</v>
+        <v>0.1479663369959274</v>
       </c>
       <c r="D3" t="n">
-        <v>3.241692721843719</v>
+        <v>1.336945652961731</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1975764625031617</v>
+        <v>0.06624418526793617</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1197154339247501</v>
+        <v>0.08172215172799123</v>
       </c>
     </row>
     <row r="4">
@@ -2632,85 +3414,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.040553645936589</v>
+        <v>0.6084318380223158</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2026350265682765</v>
+        <v>0.1521086304238837</v>
       </c>
       <c r="D4" t="n">
-        <v>5.199420809745789</v>
+        <v>1.486804008483887</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3168971456587126</v>
+        <v>0.07366950180579704</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1142621190904361</v>
+        <v>0.07843912861808669</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>구경(m)_정규화</t>
+          <t>지반 조건_정규화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5951155393217926</v>
+        <v>0.3062467494100243</v>
       </c>
       <c r="C5" t="n">
-        <v>0.115891432981452</v>
+        <v>0.07656202505105686</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5790590643882751</v>
+        <v>3.060022637248039</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03529280883141692</v>
+        <v>0.151620752913088</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08059862415003503</v>
+        <v>0.07505872786203119</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>시공 위치_정규화</t>
+          <t>요구사항_보조정규화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7670897370107697</v>
+        <v>0.7832845266423945</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1493812931667936</v>
+        <v>0.1958219953891117</v>
       </c>
       <c r="D6" t="n">
-        <v>3.744552612304688</v>
+        <v>2.762166917324066</v>
       </c>
       <c r="E6" t="n">
-        <v>0.228225042370873</v>
+        <v>0.1368623298986239</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07884374920407933</v>
+        <v>0.05895966549048778</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>심도(m)_정규화</t>
+          <t>구경(m)_정규화</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6658520121865263</v>
+        <v>0.3426556591120367</v>
       </c>
       <c r="C7" t="n">
-        <v>0.129666491205759</v>
+        <v>0.08566429262469563</v>
       </c>
       <c r="D7" t="n">
-        <v>1.007269024848938</v>
+        <v>0.6202138662338257</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06139158390233656</v>
+        <v>0.03073091428175845</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06827490730342242</v>
+        <v>0.05493337834293718</v>
       </c>
     </row>
     <row r="8">
@@ -2720,19 +3502,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1622161721846398</v>
+        <v>0.01889102009804899</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03158960471552828</v>
+        <v>0.004722775855656162</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4077300727367401</v>
+        <v>0.5359050631523132</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02485055566329695</v>
+        <v>0.02655350590417983</v>
       </c>
       <c r="F8" t="n">
-        <v>0.006739049052231331</v>
+        <v>0.02183073004852366</v>
       </c>
     </row>
     <row r="9">
@@ -2742,19 +3524,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6187573660755248</v>
+        <v>0.5333896598625405</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1204953880116158</v>
+        <v>0.1333480031348663</v>
       </c>
       <c r="D9" t="n">
-        <v>1.990365535020828</v>
+        <v>2.690399169921875</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1213098881481792</v>
+        <v>0.1333063170235745</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0008145001365633536</v>
+        <v>4.168611129173883e-05</v>
       </c>
     </row>
   </sheetData>
